--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BGDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AR\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C675A6B7-1944-4BEB-ADA5-F2D2872020CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD250923-EF19-4B62-BF55-F45956C47CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13395" yWindow="345" windowWidth="15360" windowHeight="16755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Notes:</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
   </si>
 </sst>
 </file>
@@ -277,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -293,6 +296,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,18 +601,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="7">
+        <v>45236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -616,37 +626,37 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -4922,112 +4932,112 @@
         <v>53</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
@@ -5035,112 +5045,112 @@
         <v>54</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
@@ -5148,112 +5158,112 @@
         <v>55</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
@@ -5261,112 +5271,112 @@
         <v>56</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.25">

--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AR\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD250923-EF19-4B62-BF55-F45956C47CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66965E0E-7832-46B3-BBDF-CDBF33B6BE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13395" yWindow="345" windowWidth="15360" windowHeight="16755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="17430" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>60</v>
       </c>
       <c r="C1" s="7">
-        <v>45236</v>
+        <v>45272</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="J3:AK10" si="1">$B3</f>
+        <f t="shared" ref="J3:AK9" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="T3">
@@ -3144,140 +3144,112 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
@@ -3708,140 +3680,112 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10">
-        <f t="shared" ref="G10:AK15" si="2">$B10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -3849,138 +3793,112 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
@@ -3992,143 +3910,143 @@
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:I12" si="3">$B12</f>
+        <f t="shared" ref="C12:I12" si="2">$B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G12:AK15" si="3">$B12</f>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.6003999999999998E-2</v>
       </c>
     </row>
@@ -4152,127 +4070,127 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4305,115 +4223,115 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4449,111 +4367,111 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>

--- a/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/BGDPbES/BAU Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AR\elec\BGDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66965E0E-7832-46B3-BBDF-CDBF33B6BE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{153B0C0D-4039-4888-BA64-42105CFE91E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="17430" windowHeight="17160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="660" windowWidth="16755" windowHeight="14505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>60</v>
       </c>
       <c r="C1" s="7">
-        <v>45272</v>
+        <v>45293</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
